--- a/changes/foregrips.xlsx
+++ b/changes/foregrips.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{786D04E8-B896-4C4A-BEB9-53D6EFFC6CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444B776-318B-4915-A73B-4EE42294B0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -314,9 +314,6 @@
     <t>launchtron_psrl_plastic_foregrip</t>
   </si>
   <si>
-    <t>overlord_halo</t>
-  </si>
-  <si>
     <t>Overlord HALO MLOK Handstop</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>LaunchTron USA PSRL Plastic</t>
+  </si>
+  <si>
+    <t>overlord_halo_mlok_handstop</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1235,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1262,7 +1262,7 @@
         <v>32</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1316,7 +1316,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1343,7 +1343,7 @@
         <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1370,7 +1370,7 @@
         <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1397,7 +1397,7 @@
         <v>36</v>
       </c>
       <c r="B9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1424,7 +1424,7 @@
         <v>37</v>
       </c>
       <c r="B10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1451,7 +1451,7 @@
         <v>38</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1478,7 +1478,7 @@
         <v>39</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1505,7 +1505,7 @@
         <v>40</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -1532,7 +1532,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" t="s">
         <v>95</v>
-      </c>
-      <c r="B15" t="s">
-        <v>96</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" t="s">
         <v>93</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1613,7 +1613,7 @@
         <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1748,7 +1748,7 @@
         <v>47</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -1775,7 +1775,7 @@
         <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C24">
         <v>-3</v>
@@ -1829,7 +1829,7 @@
         <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -1856,7 +1856,7 @@
         <v>51</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1883,7 +1883,7 @@
         <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -1910,7 +1910,7 @@
         <v>53</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1937,7 +1937,7 @@
         <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1964,7 +1964,7 @@
         <v>55</v>
       </c>
       <c r="B31" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -1991,7 +1991,7 @@
         <v>56</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C32">
         <v>4</v>
@@ -2018,7 +2018,7 @@
         <v>57</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -2045,7 +2045,7 @@
         <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2072,7 +2072,7 @@
         <v>59</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -2099,7 +2099,7 @@
         <v>60</v>
       </c>
       <c r="B36" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -2126,7 +2126,7 @@
         <v>61</v>
       </c>
       <c r="B37" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -2153,7 +2153,7 @@
         <v>62</v>
       </c>
       <c r="B38" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2180,7 +2180,7 @@
         <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -2207,7 +2207,7 @@
         <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -2234,7 +2234,7 @@
         <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -2261,7 +2261,7 @@
         <v>66</v>
       </c>
       <c r="B42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C42">
         <v>4</v>
@@ -2288,7 +2288,7 @@
         <v>67</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2342,7 +2342,7 @@
         <v>69</v>
       </c>
       <c r="B45" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2369,7 +2369,7 @@
         <v>70</v>
       </c>
       <c r="B46" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -2396,7 +2396,7 @@
         <v>71</v>
       </c>
       <c r="B47" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -2423,7 +2423,7 @@
         <v>72</v>
       </c>
       <c r="B48" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C48">
         <v>6</v>
@@ -2450,7 +2450,7 @@
         <v>73</v>
       </c>
       <c r="B49" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C49">
         <v>6</v>
@@ -2477,7 +2477,7 @@
         <v>74</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -2605,7 +2605,7 @@
         <v>78</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -2632,7 +2632,7 @@
         <v>79</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2659,7 +2659,7 @@
         <v>80</v>
       </c>
       <c r="B57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C57">
         <v>-1</v>
@@ -2686,7 +2686,7 @@
         <v>81</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -2713,7 +2713,7 @@
         <v>82</v>
       </c>
       <c r="B59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -2740,7 +2740,7 @@
         <v>83</v>
       </c>
       <c r="B60" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2767,7 +2767,7 @@
         <v>84</v>
       </c>
       <c r="B61" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -2794,7 +2794,7 @@
         <v>85</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -2821,7 +2821,7 @@
         <v>86</v>
       </c>
       <c r="B63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C63">
         <v>-1</v>
@@ -2848,7 +2848,7 @@
         <v>87</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -2875,7 +2875,7 @@
         <v>88</v>
       </c>
       <c r="B65" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C65">
         <v>3</v>
@@ -2902,7 +2902,7 @@
         <v>89</v>
       </c>
       <c r="B66" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -2998,7 +2998,7 @@
         <v>92</v>
       </c>
       <c r="B71" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C71">
         <v>3</v>

--- a/changes/foregrips.xlsx
+++ b/changes/foregrips.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B444B776-318B-4915-A73B-4EE42294B0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEF22A4-9E5D-4AFD-BE0D-DF3462A8EC65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,9 +131,6 @@
     <t>dd_enhanced_mvg</t>
   </si>
   <si>
-    <t>magtap_mvg_mag597_foregrip</t>
-  </si>
-  <si>
     <t>okb_crazy_romanian_mlok_full_grip</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>magtap_afg_2_grip</t>
   </si>
   <si>
-    <t>magtap_rvg_mag412_foregrip</t>
-  </si>
-  <si>
     <t>mission_first_folding_grip</t>
   </si>
   <si>
@@ -326,9 +320,6 @@
     <t>AD Enhanced MVG</t>
   </si>
   <si>
-    <t>Magtap MVG MAG597</t>
-  </si>
-  <si>
     <t>OKB Crazy Romanian MLOK Full</t>
   </si>
   <si>
@@ -386,9 +377,6 @@
     <t>Magtap AFG-2</t>
   </si>
   <si>
-    <t>Magtap RVG MAG412</t>
-  </si>
-  <si>
     <t>Mission First Tactical Folding</t>
   </si>
   <si>
@@ -459,6 +447,18 @@
   </si>
   <si>
     <t>overlord_halo_mlok_handstop</t>
+  </si>
+  <si>
+    <t>magtap_rcp_mag412_foregrip</t>
+  </si>
+  <si>
+    <t>Magtap RCP MAG412</t>
+  </si>
+  <si>
+    <t>magtap_mcp_mag597_foregrip</t>
+  </si>
+  <si>
+    <t>Magtap MCP MAG597</t>
   </si>
 </sst>
 </file>
@@ -1235,7 +1235,7 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C3">
         <v>4</v>
@@ -1259,10 +1259,10 @@
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>140</v>
       </c>
       <c r="B4" t="s">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="C4">
         <v>4</v>
@@ -1286,7 +1286,7 @@
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
@@ -1313,10 +1313,10 @@
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -1394,10 +1394,10 @@
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -1421,10 +1421,10 @@
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -1448,10 +1448,10 @@
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -1475,10 +1475,10 @@
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C12">
         <v>6</v>
@@ -1502,10 +1502,10 @@
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C13">
         <v>6</v>
@@ -1532,7 +1532,7 @@
         <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C14">
         <v>6</v>
@@ -1556,10 +1556,10 @@
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C15">
         <v>6</v>
@@ -1583,10 +1583,10 @@
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -1595,25 +1595,25 @@
         <v>0.03</v>
       </c>
       <c r="E16">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="M16">
         <v>600</v>
       </c>
       <c r="N16">
         <f t="shared" si="0"/>
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -1637,7 +1637,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
         <v>20</v>
@@ -1664,7 +1664,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
         <v>21</v>
@@ -1691,7 +1691,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
         <v>22</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1745,10 +1745,10 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C23">
         <v>-1</v>
@@ -1772,10 +1772,10 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C24">
         <v>-3</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
         <v>23</v>
@@ -1826,10 +1826,10 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C26">
         <v>6</v>
@@ -1853,10 +1853,10 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C27">
         <v>1</v>
@@ -1880,10 +1880,10 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B28" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>6</v>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B29" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C29">
         <v>5</v>
@@ -1934,10 +1934,10 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C30">
         <v>2</v>
@@ -1961,10 +1961,10 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B31" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C31">
         <v>4</v>
@@ -1988,10 +1988,10 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C32">
         <v>4</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -2042,10 +2042,10 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B34" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C34">
         <v>1</v>
@@ -2069,10 +2069,10 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B35" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C35">
         <v>4</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B36" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -2123,10 +2123,10 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C37">
         <v>4</v>
@@ -2150,10 +2150,10 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B38" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C38">
         <v>2</v>
@@ -2177,10 +2177,10 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B39" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -2204,10 +2204,10 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -2258,10 +2258,10 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B42" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C42">
         <v>4</v>
@@ -2285,10 +2285,10 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C43">
         <v>5</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B44" t="s">
         <v>24</v>
@@ -2339,10 +2339,10 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -2366,10 +2366,10 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C46">
         <v>5</v>
@@ -2393,10 +2393,10 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -2420,10 +2420,10 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C48">
         <v>6</v>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B49" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C49">
         <v>6</v>
@@ -2474,10 +2474,10 @@
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B50" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C50">
         <v>4</v>
@@ -2521,7 +2521,7 @@
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B52" t="s">
         <v>25</v>
@@ -2548,7 +2548,7 @@
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B53" t="s">
         <v>26</v>
@@ -2575,7 +2575,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B54" t="s">
         <v>27</v>
@@ -2602,10 +2602,10 @@
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B57" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C57">
         <v>-1</v>
@@ -2683,10 +2683,10 @@
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B58" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C58">
         <v>4</v>
@@ -2710,10 +2710,10 @@
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -2737,10 +2737,10 @@
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B60" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C60">
         <v>5</v>
@@ -2764,10 +2764,10 @@
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B61" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -2791,10 +2791,10 @@
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B63" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C63">
         <v>-1</v>
@@ -2845,10 +2845,10 @@
     </row>
     <row r="64" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B64" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C64">
         <v>4</v>
@@ -2872,10 +2872,10 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B65" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C65">
         <v>3</v>
@@ -2899,10 +2899,10 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B66" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C66">
         <v>5</v>
@@ -2932,7 +2932,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B68" t="s">
         <v>28</v>
@@ -2959,7 +2959,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B69" t="s">
         <v>29</v>
@@ -2995,10 +2995,10 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B71" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C71">
         <v>3</v>
